--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron. Elle dit : c'est une surprise gentille. On la garde un peu. Didier sent le citron. Il a envie de parler. Maman dit : on garde un peu. Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table. Didier dit : c'est pour toi, papa. Puis on dit. Papa ouvre les yeux. Il rit. Didier dit : c'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
+          <t>C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron. C'est une surprise gentille. On la garde un peu. Didier sent le citron. Il a envie de parler. On garde un peu. Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table. C'est pour toi, papa. Puis on dit. Papa ouvre les yeux. Il rit. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron.
+narrateur|C'est une surprise gentille. On la garde un peu.
+narrateur|Didier sent le citron. Il a envie de parler.
+maman|On garde un peu.
+narrateur|Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table.
+enfant-m|C'est pour toi, papa.
+narrateur|Puis on dit. Papa ouvre les yeux. Il rit.
+enfant-m|C'était une surprise gentille. On l'a gardée un peu.
+narrateur|Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Didier a une surprise gentille. Que fait-on ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Didier a gardé la surprise gentille. Puis on a dit. Papa a souri.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Didier goûte une miette. Le citron est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Didier a une surprise gentille. Que fait-on ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Didier a gardé la surprise gentille. Puis on a dit. Papa a souri.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Didier goûte une miette. Le citron est doux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Didier garde la surprise gentille</t>
+          <t>Le gâteau caché de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino sent le gâteau au citron. Il a envie de parler. Il garde un peu. Papa rentre. Puis on dit.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron. C'est une surprise gentille. On la garde un peu. Didier sent le citron. Il a envie de parler. On garde un peu. Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table. C'est pour toi, papa. Puis on dit. Papa ouvre les yeux. Il rit. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
+          <t>Une odeur de citron reste dans l'air. Le four est encore tiède. Un torchon blanc cache quelque chose. Des zestes jaunes dorment dans une assiette. Le couvercle de la casserole est tiède. Une cuillère en bois repose, un peu collante. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,70 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron.
-narrateur|C'est une surprise gentille. On la garde un peu.
-narrateur|Didier sent le citron. Il a envie de parler.
+          <t>narrateur|Une odeur de citron reste dans l'air.
+narrateur|Le four est encore tiède.
+narrateur|Un torchon blanc cache quelque chose.
+narrateur|Des zestes jaunes dorment dans une assiette.
+narrateur|Le couvercle de la casserole est tiède.
+narrateur|Une cuillère en bois repose, un peu collante.
+narrateur|La cuisine est calme, tout doux.
+maman|Tu as les mains propres, Nino ?
+enfant-m|Oui, maman.
+narrateur|Maman essuie le plan de travail.
+maman|Nino, tu sens le citron ?
+enfant-m|Oui, fort.
+narrateur|Papa n'est pas encore là.
+narrateur|On entend ses pas, tout loin, dans la rue.
+maman|Bientôt, c'est l'anniversaire de papa.
+maman|Le gâteau est prêt.
+enfant-m|Il est sous le torchon ?
+maman|Oui.
+narrateur|En ce moment, maman soulève le torchon.
+narrateur|Le gâteau au citron est jaune, tout rond.
+enfant-m|Il est beau.
+maman|C'est une surprise gentille.
+maman|On la garde un peu.
+enfant-m|On la garde un peu.
+narrateur|Nino sent encore le citron.
+narrateur|Il a envie de parler.
 maman|On garde un peu.
-narrateur|Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table.
+maman|Puis on dit.
+enfant-m|Puis on dit.
+narrateur|Nino hoche la tête.
+maman|On remet le torchon.
+narrateur|La porte s'ouvre.
+narrateur|Papa rentre, un sac à la main.
+papa|Ça sent le citron ici.
+enfant-m|Je garde encore un peu.
+narrateur|Nino serre les lèvres.
+narrateur|Il ne parle pas du gâteau.
+narrateur|La surprise gentille reste encore.
+maman|Encore un tout petit peu.
+papa|Je pose le sac.
+narrateur|Plus tard, maman pose le gâteau sur la table.
+narrateur|Le torchon n'est plus là.
+maman|Maintenant, on dit.
 enfant-m|C'est pour toi, papa.
-narrateur|Puis on dit. Papa ouvre les yeux. Il rit.
-enfant-m|C'était une surprise gentille. On l'a gardée un peu.
-narrateur|Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+enfant-m|Surprise.
+narrateur|Papa ouvre les yeux, tout grands.
+papa|Un gâteau au citron.
+papa|Merci, Nino.
+enfant-m|C'était une surprise gentille.
+enfant-m|On l'a gardée un peu.
+maman|Puis on a dit.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Papa serre Nino, tout doux.
+narrateur|Le gâteau sent encore le citron.
+maman|Une surprise gentille se garde un peu.
+maman|Puis on dit.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Didier a une surprise gentille. Que fait-on ?</t>
+          <t>Nino a une surprise gentille. Que fait-on ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1425,7 +1489,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
@@ -1508,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Didier a une surprise gentille. Que fait-on ?</t>
+          <t>narrateur|Nino a une surprise gentille.
+narrateur|Que fait-on ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1601,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Didier a gardé la surprise gentille. Puis on a dit. Papa a souri.</t>
+          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Tu as fait du bon travail. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1745,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Didier a gardé la surprise gentille. Puis on a dit. Papa a souri.</t>
+          <t>narrateur|Nino a gardé la surprise gentille.
+narrateur|Puis on a dit.
+narrateur|Papa a vu le gâteau.
+maman|On garde un peu.
+maman|Puis on dit.
+enfant-m|Surprise gentille.
+enfant-m|Puis on dit.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Une miette tombe sur la table.
+maman|Tu as attendu le bon moment.
+enfant-m|Puis on a dit.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Didier goûte une miette. Le citron est doux.</t>
+          <t>Nino goûte une miette. Le citron est doux, un peu acide. Une petite part pour toi. Oui. Le four est froid, maintenant. Les zestes restent dans l'assiette. Tu as gardé un peu. Puis tu as dit. Même quand j'avais envie de parler. Oui. Puis le bon moment est venu. Le sac de papa est près de la porte. J'ai apporté des pommes. Après le gâteau. Après, oui. La cuillère en bois est dans l'évier. Elle n'est plus collante. On a gardé, puis on a dit. C'était le bon moment.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1920,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Didier goûte une miette. Le citron est doux.</t>
+          <t>narrateur|Nino goûte une miette.
+narrateur|Le citron est doux, un peu acide.
+papa|Une petite part pour toi.
+enfant-m|Oui.
+maman|Le four est froid, maintenant.
+narrateur|Les zestes restent dans l'assiette.
+papa|Tu as gardé un peu.
+papa|Puis tu as dit.
+enfant-m|Même quand j'avais envie de parler.
+maman|Oui.
+maman|Puis le bon moment est venu.
+narrateur|Le sac de papa est près de la porte.
+papa|J'ai apporté des pommes.
+enfant-m|Après le gâteau.
+maman|Après, oui.
+narrateur|La cuillère en bois est dans l'évier.
+enfant-m|Elle n'est plus collante.
+papa|On a gardé, puis on a dit.
+maman|C'était le bon moment.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1933,7 +2027,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
@@ -2012,7 +2106,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a gardé un peu.
+enfant-m|Puis on a dit.
+maman|Bravo, Nino.
+papa|Le citron était bon.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une odeur de citron reste dans l'air. Le four est encore tiède. Un torchon blanc cache quelque chose. Des zestes jaunes dorment dans une assiette. Le couvercle de la casserole est tiède. Une cuillère en bois repose, un peu collante. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
+          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;C'est bientôt l'anniversaire de papa. Maman sort un gâteau au citron. Elle dit : c'est une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. On la garde un peu. Didier sent le citron. Il a envie de parler. Maman dit : on garde un peu. Puis on dit. Didier hoche la tête. Papa rentre. Didier serre les lèvres. Il sourit. La surprise gentille reste encore. Plus tard, maman pose le gâteau sur la table. Didier dit : c'est pour toi, papa. Puis on dit. Papa ouvre les yeux. Il rit. Didier dit : c'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Papa serre Didier. Le gâteau sent le citron. Même leçon : une surprise gentille se garde un peu, puis on dit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,12 +1324,12 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une odeur de citron reste dans l'air.
+          <t>narrateur|Des zestes jaunes dorment dans une assiette.
+narrateur|Une cuillère en bois repose, un peu collante.
 narrateur|Le four est encore tiède.
 narrateur|Un torchon blanc cache quelque chose.
-narrateur|Des zestes jaunes dorment dans une assiette.
+narrateur|Une odeur de citron reste dans l'air.
 narrateur|Le couvercle de la casserole est tiède.
-narrateur|Une cuillère en bois repose, un peu collante.
 narrateur|La cuisine est calme, tout doux.
 maman|Tu as les mains propres, Nino ?
 enfant-m|Oui, maman.
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier a une &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. Que fait-on ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a une surprise gentille. Que fait-on ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1576,7 +1576,6 @@
 narrateur|Que fait-on ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1606,7 +1605,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier a gardé la &lt;emphasis level="moderate"&gt;surprise&lt;/emphasis&gt; gentille. Puis on a dit. Papa a souri.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Tu as fait du bon travail. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1759,7 +1758,6 @@
 enfant-m|Puis on a dit.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1789,7 +1787,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Didier goûte une miette. Le citron est doux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino goûte une miette. Le citron est doux, un peu acide. Une petite part pour toi. Oui. Le four est froid, maintenant. Les zestes restent dans l'assiette. Tu as gardé un peu. Puis tu as dit. Même quand j'avais envie de parler. Oui. Puis le bon moment est venu. Le sac de papa est près de la porte. J'ai apporté des pommes. Après le gâteau. Après, oui. La cuillère en bois est dans l'évier. Elle n'est plus collante. On a gardé, puis on a dit. C'était le bon moment.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1939,6 @@
 maman|C'était le bon moment.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1971,7 +1968,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2113,7 +2110,6 @@
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2173,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
+          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Tu as fait du bon travail. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
+          <t>Des zestes jaunes dorment dans une assiette. Une cuillère en bois repose, un peu collante. Le four est encore tiède. Un torchon blanc cache quelque chose. Une odeur de citron reste dans l'air. Le couvercle de la casserole est tiède. La cuisine est calme, tout doux. Tu as les mains propres, Nino ? Oui, maman. Maman essuie le plan de travail. Nino, tu sens le citron ? Oui, fort. Papa n'est pas encore là. On entend ses pas, tout loin, dans la rue. Bientôt, c'est l'anniversaire de papa. Le gâteau est prêt. Il est sous le torchon ? Oui. En ce moment, maman soulève le torchon. Le gâteau au citron est jaune, tout rond. Il est beau. C'est une surprise gentille. On la garde un peu. On la garde un peu. Nino sent encore le citron. Il a envie de parler. On garde un peu. Puis on dit. Puis on dit. Nino hoche la tête. On remet le torchon. La porte s'ouvre. Papa rentre, un sac à la main. Ça sent le citron ici. Je garde encore un peu. Nino serre les lèvres. Il ne parle pas du gâteau. La surprise gentille reste encore. Encore un tout petit peu. Je pose le sac. Plus tard, maman pose le gâteau sur la table. Le torchon n'est plus là. Maintenant, on dit. C'est pour toi, papa. Surprise. Papa ouvre les yeux, tout grands. Un gâteau au citron. Merci, Nino. C'était une surprise gentille. On l'a gardée un peu. Puis on a dit. Bravo, Nino. Papa serre Nino, tout doux. Le gâteau sent encore le citron. Une surprise gentille se garde un peu. Puis on dit.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,7 +1376,6 @@
 enfant-m|On l'a gardée un peu.
 maman|Puis on a dit.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
 narrateur|Papa serre Nino, tout doux.
 narrateur|Le gâteau sent encore le citron.
 maman|Une surprise gentille se garde un peu.
@@ -1600,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Tu as fait du bon travail. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
+          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Tu as fait du bon travail. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
+          <t>Nino a gardé la surprise gentille. Puis on a dit. Papa a vu le gâteau. On garde un peu. Puis on dit. Surprise gentille. Puis on dit. Bravo, Nino. Une miette tombe sur la table. Tu as attendu le bon moment. Puis on a dit.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1752,7 +1751,6 @@
 enfant-m|Surprise gentille.
 enfant-m|Puis on dit.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
 narrateur|Une miette tombe sur la table.
 maman|Tu as attendu le bon moment.
 enfant-m|Puis on a dit.</t>
@@ -1963,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon. L'histoire est finie.</t>
+          <t>On a gardé un peu. Puis on a dit. Bravo, Nino. Le citron était bon.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,8 +2104,7 @@
           <t>enfant-m|On a gardé un peu.
 enfant-m|Puis on a dit.
 maman|Bravo, Nino.
-papa|Le citron était bon.
-narrateur|L'histoire est finie.</t>
+papa|Le citron était bon.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2175,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
+++ b/stories/arbres/ATOM-FAM.SEC.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Didier, maman, papa</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>
